--- a/sample_dictionary.xlsx
+++ b/sample_dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priha\OneDrive - Office's ID\Documents\DICTIONARY-LAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947379E5-9D69-4D16-AD49-36B235D54D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C61E050-FCA1-4521-9060-47536D535655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
   <si>
     <t>general_word</t>
   </si>
@@ -335,6 +335,12 @@
   </si>
   <si>
     <t>sense1_trigram</t>
+  </si>
+  <si>
+    <t>general_wordlist</t>
+  </si>
+  <si>
+    <t>NGSL=12;CEFR=B2;Academic=12</t>
   </si>
 </sst>
 </file>
@@ -685,13 +691,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="20" max="20" width="12.796875" customWidth="1"/>
+    <col min="21" max="21" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,121 +735,124 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -881,85 +890,88 @@
         <v>51</v>
       </c>
       <c r="M2" t="s">
+        <v>106</v>
+      </c>
+      <c r="N2" t="s">
         <v>52</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>53</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>70</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>26.6</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>3.9</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>4</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>98</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>102</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>54</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>55</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>56</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>59</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>60</v>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <v>50</v>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <v>19</v>
       </c>
-      <c r="AE2">
+      <c r="AF2">
         <v>3.6</v>
       </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>4</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>61</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>62</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>63</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>64</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>58</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -990,80 +1002,80 @@
       <c r="L3" t="s">
         <v>71</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>66</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>60</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>220</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>80.7</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>4.7</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>72</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>73</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>74</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>75</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>76</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>77</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>66</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>60</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>80</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>29.5</v>
-      </c>
-      <c r="AE3">
-        <v>4</v>
       </c>
       <c r="AF3">
         <v>4</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AG3">
+        <v>4</v>
+      </c>
+      <c r="AH3" t="s">
         <v>78</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>79</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>80</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>57</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>58</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AM3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -1094,76 +1106,76 @@
       <c r="L4" t="s">
         <v>87</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>82</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>53</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>350</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>126.2</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>5</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>3</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>88</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>89</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>90</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>57</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>82</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>60</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>150</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>54.1</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AF4">
+      <c r="AG4">
         <v>4</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>93</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>94</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>95</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>96</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>97</v>
       </c>
     </row>

--- a/sample_dictionary.xlsx
+++ b/sample_dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priha\OneDrive - Office's ID\Documents\DICTIONARY-LAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C61E050-FCA1-4521-9060-47536D535655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92C295C-E1C7-4463-B8CB-890374BC2772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
   <si>
     <t>general_word</t>
   </si>
@@ -341,6 +341,18 @@
   </si>
   <si>
     <t>NGSL=12;CEFR=B2;Academic=12</t>
+  </si>
+  <si>
+    <t>sense1_pronounciation</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>general_pronunciation</t>
+  </si>
+  <si>
+    <t>sau</t>
   </si>
 </sst>
 </file>
@@ -691,491 +703,503 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:BA4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="21" max="21" width="12.796875" customWidth="1"/>
+    <col min="23" max="23" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:53" s="1" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>46</v>
       </c>
       <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
         <v>47</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>120</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>45.6</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>4.2</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>98</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>99</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>48</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>49</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>50</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>51</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>106</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>52</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q2" t="s">
         <v>53</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>70</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>26.6</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>3.9</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>4</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>98</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>102</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>54</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>55</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>58</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>46</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>60</v>
       </c>
-      <c r="AD2">
+      <c r="AF2">
         <v>50</v>
       </c>
-      <c r="AE2">
+      <c r="AG2">
         <v>19</v>
       </c>
-      <c r="AF2">
+      <c r="AH2">
         <v>3.6</v>
       </c>
-      <c r="AG2">
+      <c r="AI2">
         <v>4</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>61</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>62</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>63</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" t="s">
         <v>64</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AN2" t="s">
         <v>58</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AO2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>66</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>67</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>300</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>110.2</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>3</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>68</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>69</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>70</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>71</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>66</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>60</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>220</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>80.7</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>4.7</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>3</v>
       </c>
-      <c r="V3" t="s">
+      <c r="X3" t="s">
         <v>72</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>73</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>74</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" t="s">
         <v>75</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
         <v>76</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>77</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>66</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE3" t="s">
         <v>60</v>
       </c>
-      <c r="AD3">
+      <c r="AF3">
         <v>80</v>
       </c>
-      <c r="AE3">
+      <c r="AG3">
         <v>29.5</v>
       </c>
-      <c r="AF3">
+      <c r="AH3">
         <v>4</v>
       </c>
-      <c r="AG3">
+      <c r="AI3">
         <v>4</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AJ3" t="s">
         <v>78</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AK3" t="s">
         <v>79</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AL3" t="s">
         <v>80</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AM3" t="s">
         <v>57</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AN3" t="s">
         <v>58</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AO3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>82</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>83</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>500</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>180.3</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>5.3</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>84</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>85</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>86</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>87</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>82</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>53</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>350</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>126.2</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>5</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>3</v>
       </c>
-      <c r="V4" t="s">
+      <c r="X4" t="s">
         <v>88</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Y4" t="s">
         <v>89</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Z4" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AA4" t="s">
         <v>57</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AB4" t="s">
         <v>91</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AC4" t="s">
         <v>92</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AD4" t="s">
         <v>82</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
         <v>60</v>
       </c>
-      <c r="AD4">
+      <c r="AF4">
         <v>150</v>
       </c>
-      <c r="AE4">
+      <c r="AG4">
         <v>54.1</v>
       </c>
-      <c r="AF4">
+      <c r="AH4">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AG4">
+      <c r="AI4">
         <v>4</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AJ4" t="s">
         <v>93</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AK4" t="s">
         <v>94</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AL4" t="s">
         <v>95</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AM4" t="s">
         <v>96</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AN4" t="s">
         <v>58</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AO4" t="s">
         <v>97</v>
       </c>
     </row>
